--- a/data/trans_camb/P2A_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 12,8</t>
+          <t>-0,64; 12,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 7,67</t>
+          <t>-6,87; 7,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,13; -0,95</t>
+          <t>-13,52; -0,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 10,58</t>
+          <t>-5,73; 10,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 9,18</t>
+          <t>-6,44; 9,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,77; -4,68</t>
+          <t>-18,44; -5,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 9,86</t>
+          <t>-0,53; 10,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 6,71</t>
+          <t>-3,73; 6,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,65; -4,66</t>
+          <t>-13,99; -4,3</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 30,57</t>
+          <t>-1,43; 30,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 18,0</t>
+          <t>-13,63; 18,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-27,53; -2,3</t>
+          <t>-27,65; -0,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 22,87</t>
+          <t>-10,46; 21,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 19,84</t>
+          <t>-12,04; 19,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,38; -10,39</t>
+          <t>-33,49; -10,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 21,74</t>
+          <t>-1,05; 22,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 14,96</t>
+          <t>-7,35; 14,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-26,9; -10,21</t>
+          <t>-28,07; -9,42</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 13,07</t>
+          <t>-0,91; 13,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 8,92</t>
+          <t>-6,23; 9,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,92; -5,69</t>
+          <t>-19,22; -5,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 14,38</t>
+          <t>-0,79; 14,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 3,27</t>
+          <t>-11,49; 2,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,12; -11,92</t>
+          <t>-25,72; -12,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 11,54</t>
+          <t>1,15; 11,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 3,56</t>
+          <t>-6,64; 4,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-20,55; -11,02</t>
+          <t>-20,56; -10,84</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 29,81</t>
+          <t>-1,63; 32,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 20,83</t>
+          <t>-12,08; 20,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,53; -12,81</t>
+          <t>-37,26; -12,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 27,61</t>
+          <t>-1,38; 27,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 6,27</t>
+          <t>-19,75; 5,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,86; -23,62</t>
+          <t>-43,47; -24,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 23,99</t>
+          <t>2,25; 23,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 7,4</t>
+          <t>-12,16; 9,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-38,0; -22,53</t>
+          <t>-37,78; -22,2</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,12; 16,24</t>
+          <t>4,68; 16,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,97; 16,58</t>
+          <t>4,16; 15,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-41,26; -6,18</t>
+          <t>-39,21; -5,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 17,56</t>
+          <t>-0,76; 18,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 13,7</t>
+          <t>-5,94; 15,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,16; -1,04</t>
+          <t>-20,97; -1,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,36; 15,51</t>
+          <t>5,93; 15,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,33; 14,23</t>
+          <t>3,57; 14,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-41,24; -7,11</t>
+          <t>-39,15; -7,01</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,49; 36,26</t>
+          <t>9,23; 35,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,56; 36,02</t>
+          <t>8,05; 35,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-80,84; -13,19</t>
+          <t>-77,85; -12,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 31,62</t>
+          <t>-1,09; 32,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 24,03</t>
+          <t>-8,87; 27,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-30,05; -1,79</t>
+          <t>-30,5; -2,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,75; 31,73</t>
+          <t>10,8; 31,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,01; 29,25</t>
+          <t>6,43; 28,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-76,33; -13,64</t>
+          <t>-71,8; -13,55</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,45; 9,95</t>
+          <t>1,51; 9,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 6,09</t>
+          <t>-2,12; 5,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,39; -4,62</t>
+          <t>-13,12; -4,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 8,53</t>
+          <t>-2,41; 7,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,88; -0,86</t>
+          <t>-10,19; -0,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,27; 15,04</t>
+          <t>-20,83; 13,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,68; 8,07</t>
+          <t>1,74; 7,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 2,23</t>
+          <t>-4,13; 2,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 7,24</t>
+          <t>-13,81; 9,39</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,62; 19,35</t>
+          <t>2,89; 19,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 11,93</t>
+          <t>-3,84; 11,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-24,53; -9,08</t>
+          <t>-24,31; -8,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 14,37</t>
+          <t>-3,74; 12,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-16,84; -1,72</t>
+          <t>-15,93; -1,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-33,62; 24,86</t>
+          <t>-33,15; 22,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,8; 14,77</t>
+          <t>3,02; 14,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 4,14</t>
+          <t>-7,1; 4,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-24,5; 12,94</t>
+          <t>-24,38; 17,26</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 12,76</t>
+          <t>-0,57; 13,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 10,66</t>
+          <t>-3,81; 10,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 3,14</t>
+          <t>-11,56; 3,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,74; 15,13</t>
+          <t>4,93; 15,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,14; 13,5</t>
+          <t>3,14; 13,78</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-29,49; -9,86</t>
+          <t>-29,55; -9,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,95; 12,38</t>
+          <t>3,5; 12,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 9,46</t>
+          <t>0,55; 9,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-20,57; -6,81</t>
+          <t>-22,11; -6,83</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 26,52</t>
+          <t>-0,98; 28,91</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 22,07</t>
+          <t>-6,62; 21,46</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-19,72; 6,39</t>
+          <t>-20,4; 7,39</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6,91; 24,21</t>
+          <t>7,3; 24,69</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4,63; 21,97</t>
+          <t>4,58; 22,21</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-45,53; -15,64</t>
+          <t>-44,32; -14,24</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,35; 21,19</t>
+          <t>5,41; 21,68</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1,69; 16,31</t>
+          <t>0,94; 15,72</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-33,91; -11,88</t>
+          <t>-35,33; -11,83</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3,1; 18,56</t>
+          <t>3,41; 18,97</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,5; 15,1</t>
+          <t>-0,12; 15,31</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 10,1</t>
+          <t>-10,57; 11,92</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,29; 7,86</t>
+          <t>0,43; 8,04</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 3,68</t>
+          <t>-3,9; 3,7</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-21,84; -13,53</t>
+          <t>-22,23; -13,47</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,61; 8,99</t>
+          <t>1,36; 8,82</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 4,41</t>
+          <t>-2,78; 4,28</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-19,8; -11,1</t>
+          <t>-20,25; -11,31</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>10,36; 78,92</t>
+          <t>10,7; 79,68</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1,58; 64,81</t>
+          <t>-1,03; 62,62</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-35,06; 41,56</t>
+          <t>-35,1; 48,11</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0,41; 11,66</t>
+          <t>0,66; 11,96</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 5,32</t>
+          <t>-5,44; 5,42</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-30,66; -19,76</t>
+          <t>-31,21; -19,72</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,55; 14,93</t>
+          <t>2,13; 14,83</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 7,29</t>
+          <t>-4,37; 7,1</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-31,31; -18,48</t>
+          <t>-32,18; -18,69</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>4,97; 9,88</t>
+          <t>4,95; 9,77</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,75</t>
+          <t>1,75; 6,67</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-18,64; -6,4</t>
+          <t>-18,48; -6,46</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,04; 7,59</t>
+          <t>3,0; 7,57</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 2,08</t>
+          <t>-2,66; 2,08</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-19,48; -4,4</t>
+          <t>-19,26; -5,56</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,57; 7,9</t>
+          <t>4,84; 8,19</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,6</t>
+          <t>0,24; 3,66</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-17,74; -7,94</t>
+          <t>-17,35; -7,81</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>10,17; 21,18</t>
+          <t>10,18; 21,01</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3,97; 14,49</t>
+          <t>3,56; 14,24</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-38,2; -13,56</t>
+          <t>-37,9; -13,69</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4,65; 11,99</t>
+          <t>4,67; 12,18</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 3,32</t>
+          <t>-4,12; 3,34</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-30,55; -7,08</t>
+          <t>-29,97; -8,82</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,06; 14,31</t>
+          <t>8,47; 14,88</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0,4; 6,48</t>
+          <t>0,43; 6,63</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-31,37; -14,19</t>
+          <t>-30,73; -13,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-7,22</t>
+          <t>-7,46</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-12,03</t>
+          <t>-11,94</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-9,01</t>
+          <t>-9,09</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 12,42</t>
+          <t>-0,3; 12,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 7,74</t>
+          <t>-5,39; 8,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,52; -0,28</t>
+          <t>-13,77; -1,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 10,25</t>
+          <t>-6,76; 10,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 9,18</t>
+          <t>-7,35; 8,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,44; -5,08</t>
+          <t>-19,02; -4,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 10,24</t>
+          <t>-0,37; 10,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 6,52</t>
+          <t>-3,86; 6,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,99; -4,3</t>
+          <t>-13,72; -4,34</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-16,0%</t>
+          <t>-16,55%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-23,48%</t>
+          <t>-23,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-18,96%</t>
+          <t>-19,14%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 30,07</t>
+          <t>-0,65; 30,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 18,39</t>
+          <t>-11,05; 19,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-27,65; -0,55</t>
+          <t>-28,87; -2,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 21,32</t>
+          <t>-11,85; 23,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 19,62</t>
+          <t>-13,21; 17,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,49; -10,36</t>
+          <t>-34,23; -10,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 22,78</t>
+          <t>-0,99; 22,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 14,29</t>
+          <t>-7,6; 14,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-28,07; -9,42</t>
+          <t>-27,25; -9,48</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-12,28</t>
+          <t>-13,12</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-18,99</t>
+          <t>-19,48</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-15,71</t>
+          <t>-16,38</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 13,61</t>
+          <t>-1,22; 13,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 9,03</t>
+          <t>-5,55; 9,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,22; -5,12</t>
+          <t>-20,14; -6,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 14,24</t>
+          <t>-0,3; 14,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 2,77</t>
+          <t>-12,13; 2,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,72; -12,74</t>
+          <t>-25,87; -12,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 11,35</t>
+          <t>0,67; 11,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 4,37</t>
+          <t>-6,39; 4,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-20,56; -10,84</t>
+          <t>-21,44; -11,52</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-25,87%</t>
+          <t>-27,65%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-34,25%</t>
+          <t>-35,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-30,53%</t>
+          <t>-31,83%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 32,15</t>
+          <t>-2,4; 30,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 20,27</t>
+          <t>-10,79; 23,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-37,26; -12,27</t>
+          <t>-39,36; -14,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 27,01</t>
+          <t>-0,49; 28,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,75; 5,24</t>
+          <t>-20,61; 5,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,47; -24,24</t>
+          <t>-43,54; -24,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 23,43</t>
+          <t>1,22; 23,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 9,07</t>
+          <t>-11,9; 8,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-37,78; -22,2</t>
+          <t>-39,17; -23,74</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-22,9</t>
+          <t>-9,18</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-11,26</t>
+          <t>-11,73</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-21,06</t>
+          <t>-9,26</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,68; 16,28</t>
+          <t>4,65; 15,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,16; 15,99</t>
+          <t>3,94; 16,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-39,21; -5,8</t>
+          <t>-16,23; -3,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 18,26</t>
+          <t>-1,14; 17,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 15,48</t>
+          <t>-6,36; 13,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,97; -1,21</t>
+          <t>-20,94; -2,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,93; 15,25</t>
+          <t>5,7; 15,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 14,12</t>
+          <t>3,86; 15,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-39,15; -7,01</t>
+          <t>-14,3; -4,01</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-47,05%</t>
+          <t>-18,87%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-18,14%</t>
+          <t>-18,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-40,63%</t>
+          <t>-17,86%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,23; 35,97</t>
+          <t>8,81; 35,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,05; 35,75</t>
+          <t>8,11; 36,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-77,85; -12,45</t>
+          <t>-30,88; -6,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 32,3</t>
+          <t>-1,65; 31,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 27,01</t>
+          <t>-9,56; 24,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-30,5; -2,02</t>
+          <t>-31,21; -3,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,8; 31,38</t>
+          <t>10,3; 31,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,43; 28,72</t>
+          <t>7,13; 30,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-71,8; -13,55</t>
+          <t>-26,2; -8,51</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-9,01</t>
+          <t>-10,12</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-7,3</t>
+          <t>-19,76</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-7,07</t>
+          <t>-13,67</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 9,88</t>
+          <t>1,69; 9,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 5,95</t>
+          <t>-2,15; 5,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,12; -4,45</t>
+          <t>-14,22; -5,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 7,73</t>
+          <t>-2,53; 8,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,19; -0,73</t>
+          <t>-10,74; -0,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,83; 13,48</t>
+          <t>-24,77; -14,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 7,85</t>
+          <t>1,72; 7,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 2,46</t>
+          <t>-3,92; 2,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,81; 9,39</t>
+          <t>-16,84; -10,63</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-17,01%</t>
+          <t>-19,09%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-11,73%</t>
+          <t>-31,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-12,54%</t>
+          <t>-24,25%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,89; 19,57</t>
+          <t>3,07; 19,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 11,41</t>
+          <t>-4,01; 11,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-24,31; -8,87</t>
+          <t>-26,2; -11,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 12,98</t>
+          <t>-3,85; 13,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,93; -1,16</t>
+          <t>-16,45; -1,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-33,15; 22,82</t>
+          <t>-38,36; -24,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,02; 14,59</t>
+          <t>3,03; 14,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 4,48</t>
+          <t>-6,74; 4,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-24,38; 17,26</t>
+          <t>-29,07; -19,32</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-3,98</t>
+          <t>-8,92</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-17,02</t>
+          <t>-12,1</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-12,06</t>
+          <t>-11,11</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 13,88</t>
+          <t>-1,7; 12,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 10,34</t>
+          <t>-3,1; 10,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 3,7</t>
+          <t>-16,1; -1,98</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,93; 15,21</t>
+          <t>4,47; 14,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,14; 13,78</t>
+          <t>3,01; 13,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-29,55; -9,2</t>
+          <t>-16,56; -6,8</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,5; 12,52</t>
+          <t>4,14; 12,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,55; 9,22</t>
+          <t>1,11; 9,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-22,11; -6,83</t>
+          <t>-15,14; -6,81</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-7,53%</t>
+          <t>-16,87%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-26,1%</t>
+          <t>-18,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-19,93%</t>
+          <t>-18,37%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 28,91</t>
+          <t>-2,98; 26,21</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 21,46</t>
+          <t>-5,34; 21,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,4; 7,39</t>
+          <t>-28,27; -4,08</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7,3; 24,69</t>
+          <t>6,52; 24,33</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4,58; 22,21</t>
+          <t>4,39; 21,36</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-44,32; -14,24</t>
+          <t>-24,69; -11,37</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,41; 21,68</t>
+          <t>6,6; 22,49</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,94; 15,72</t>
+          <t>1,81; 16,37</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-35,33; -11,83</t>
+          <t>-24,1; -11,92</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>-2,13</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-17,68</t>
+          <t>-18,18</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-15,51</t>
+          <t>-15,79</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3,41; 18,97</t>
+          <t>2,85; 19,02</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 15,31</t>
+          <t>-0,92; 14,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 11,92</t>
+          <t>-10,76; 8,6</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,43; 8,04</t>
+          <t>-0,26; 7,51</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 3,7</t>
+          <t>-3,78; 3,84</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-22,23; -13,47</t>
+          <t>-22,67; -14,02</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,36; 8,82</t>
+          <t>1,72; 8,45</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 4,28</t>
+          <t>-2,29; 4,62</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-20,25; -11,31</t>
+          <t>-19,81; -11,5</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-0,91%</t>
+          <t>-7,77%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-25,26%</t>
+          <t>-25,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-25,11%</t>
+          <t>-25,57%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>10,7; 79,68</t>
+          <t>9,97; 82,77</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 62,62</t>
+          <t>-2,49; 58,89</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-35,1; 48,11</t>
+          <t>-36,65; 37,26</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0,66; 11,96</t>
+          <t>-0,34; 11,0</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 5,42</t>
+          <t>-5,29; 5,7</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-31,21; -19,72</t>
+          <t>-31,96; -20,45</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,13; 14,83</t>
+          <t>2,77; 14,05</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 7,1</t>
+          <t>-3,66; 7,74</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-32,18; -18,69</t>
+          <t>-31,46; -19,29</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-10,39</t>
+          <t>-8,83</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-15,19</t>
+          <t>-17,55</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-12,76</t>
+          <t>-13,22</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>4,95; 9,77</t>
+          <t>4,97; 9,93</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,67</t>
+          <t>1,67; 6,61</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-18,48; -6,46</t>
+          <t>-11,59; -6,42</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,0; 7,57</t>
+          <t>3,07; 7,6</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 2,08</t>
+          <t>-2,5; 2,17</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-19,26; -5,56</t>
+          <t>-19,72; -15,32</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,84; 8,19</t>
+          <t>4,73; 7,99</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,66</t>
+          <t>0,05; 3,58</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-17,35; -7,81</t>
+          <t>-14,92; -11,61</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-21,57%</t>
+          <t>-18,33%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-23,79%</t>
+          <t>-27,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-22,73%</t>
+          <t>-23,55%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>10,18; 21,01</t>
+          <t>10,11; 21,14</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3,56; 14,24</t>
+          <t>3,35; 14,1</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-37,9; -13,69</t>
+          <t>-23,52; -13,69</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4,67; 12,18</t>
+          <t>4,75; 12,14</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 3,34</t>
+          <t>-3,83; 3,48</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-29,97; -8,82</t>
+          <t>-30,27; -24,42</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,47; 14,88</t>
+          <t>8,24; 14,37</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0,43; 6,63</t>
+          <t>0,09; 6,48</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-30,73; -13,97</t>
+          <t>-26,17; -20,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación</t>
+          <t>Población que convive con personas con alguna condición, enfermedad crónica o limitación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
